--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
